--- a/artfynd/A 22230-2022 artfynd.xlsx
+++ b/artfynd/A 22230-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22230-2022 artfynd.xlsx
+++ b/artfynd/A 22230-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80108318</v>
+        <v>80108615</v>
       </c>
       <c r="B2" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229497</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>385984.9767903021</v>
+        <v>386054</v>
       </c>
       <c r="R2" t="n">
-        <v>6713400.32715701</v>
+        <v>6713434</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -749,19 +744,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80108615</v>
+        <v>80109004</v>
       </c>
       <c r="B3" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,17 +802,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kullarna , Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386053.5947697819</v>
+        <v>386059</v>
       </c>
       <c r="R3" t="n">
-        <v>6713433.611315456</v>
+        <v>6713455</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -862,19 +846,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,54 +875,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80108465</v>
+        <v>112551662</v>
       </c>
       <c r="B4" t="n">
-        <v>77595</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6450</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kullarna , Vrm</t>
+          <t>Väster Naturreservatet Kullarna, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386033.1457844153</v>
+        <v>386234</v>
       </c>
       <c r="R4" t="n">
-        <v>6713426.379009394</v>
+        <v>6713573</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,22 +940,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,66 +960,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80110315</v>
+        <v>105127729</v>
       </c>
       <c r="B5" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kullarna , Vrm</t>
+          <t>Väster om Kullarna, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>386298.4013443544</v>
+        <v>386170</v>
       </c>
       <c r="R5" t="n">
-        <v>6713643.022141684</v>
+        <v>6713525</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,22 +1037,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-12-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-12-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,66 +1057,61 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>80110283</v>
+        <v>102804581</v>
       </c>
       <c r="B6" t="n">
-        <v>77595</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kullarna , Vrm</t>
+          <t>Tjärnmyren,Torsby, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>386251.0484548907</v>
+        <v>385998</v>
       </c>
       <c r="R6" t="n">
-        <v>6713595.771617426</v>
+        <v>6713383</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,22 +1135,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,66 +1155,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Lars Tidemalm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Lars Tidemalm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>80108366</v>
+        <v>105127730</v>
       </c>
       <c r="B7" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kullarna , Vrm</t>
+          <t>Väster om Kullarna, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>386016.5916577557</v>
+        <v>386192</v>
       </c>
       <c r="R7" t="n">
-        <v>6713417.546610408</v>
+        <v>6713522</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1311,27 +1232,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-12-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Björkstubbe</t>
+          <t>2022-12-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,70 +1252,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>80109004</v>
+        <v>112551677</v>
       </c>
       <c r="B8" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kullarna , Vrm</t>
+          <t>Väster Naturreservatet Kullarna, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>386059.1895997836</v>
+        <v>386047</v>
       </c>
       <c r="R8" t="n">
-        <v>6713454.606988746</v>
+        <v>6713439</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1433,22 +1329,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,66 +1349,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>80108313</v>
+        <v>112551679</v>
       </c>
       <c r="B9" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kullarna , Vrm</t>
+          <t>Väster Naturreservatet Kullarna, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>385984.9767903021</v>
+        <v>386244</v>
       </c>
       <c r="R9" t="n">
-        <v>6713400.32715701</v>
+        <v>6713551</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1546,27 +1426,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gammal asp</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,49 +1446,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>80108359</v>
+        <v>80108465</v>
       </c>
       <c r="B10" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6450</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1634,10 +1494,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>386016.5916577557</v>
+        <v>386033</v>
       </c>
       <c r="R10" t="n">
-        <v>6713417.546610408</v>
+        <v>6713426</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1667,24 +1527,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Björkstubbe</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,15 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>80110304</v>
+        <v>80110283</v>
       </c>
       <c r="B11" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,21 +1567,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1752,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>386298.4013443544</v>
+        <v>386251</v>
       </c>
       <c r="R11" t="n">
-        <v>6713643.022141684</v>
+        <v>6713596</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1785,24 +1625,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gammal asp</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,15 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>102804581</v>
+        <v>80108313</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1845,38 +1665,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tjärnmyren,Torsby, Vrm</t>
+          <t>Kullarna , Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385998.7210970827</v>
+        <v>385985</v>
       </c>
       <c r="R12" t="n">
-        <v>6713382.659323241</v>
+        <v>6713400</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1900,22 +1720,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gammal asp</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,27 +1745,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars Tidemalm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars Tidemalm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>102936113</v>
+        <v>80109640</v>
       </c>
       <c r="B13" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1976,22 +1786,20 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kullarna NR, V om, Vrm</t>
+          <t>Kullarna , Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>386303.5881563957</v>
+        <v>386056</v>
       </c>
       <c r="R13" t="n">
-        <v>6713635.47342341</v>
+        <v>6713416</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2015,27 +1823,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Asp.</t>
+          <t>Gammal asp</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,88 +1842,67 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm, Lars Tidemalm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>102936383</v>
+        <v>80110304</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kullarna NR, V om, Vrm</t>
+          <t>Kullarna , Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>386231.3069924646</v>
+        <v>386298</v>
       </c>
       <c r="R14" t="n">
-        <v>6713579.6538354</v>
+        <v>6713643</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2149,22 +1926,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gammal asp</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,74 +1945,55 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm, Lars Tidemalm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>102938702</v>
+        <v>102936113</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2248,13 +2001,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>386177.1130995703</v>
+        <v>386304</v>
       </c>
       <c r="R15" t="n">
-        <v>6713518.832735928</v>
+        <v>6713635</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2281,24 +2034,14 @@
           <t>2022-08-10</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-08-10</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Plockhugget för länga sedan (1800-tal?). Brandstubbar.</t>
+          <t>Asp.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2326,69 +2069,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>102936371</v>
+        <v>105127732</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kullarna NR, V om, Vrm</t>
+          <t>Väster om Kullarna, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>386221.1625038022</v>
+        <v>386305</v>
       </c>
       <c r="R16" t="n">
-        <v>6713586.37439243</v>
+        <v>6713654</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2412,27 +2134,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-12-07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Barrnaturskog. Plockhugget för länge sedan (1800-tal?). Brandstubbar.</t>
+          <t>2022-12-07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2441,88 +2148,66 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm, Lars Tidemalm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>102936181</v>
+        <v>112551671</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kullarna NR, V om, Vrm</t>
+          <t>Väster Naturreservatet Kullarna, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>386254.5782055944</v>
+        <v>386309</v>
       </c>
       <c r="R17" t="n">
-        <v>6713613.877527301</v>
+        <v>6713632</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2546,27 +2231,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Plockhugget för länge sedan (1800-tal?). Brandstubbar.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2575,88 +2250,66 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm, Lars Tidemalm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>102936273</v>
+        <v>112551702</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kullarna NR, V om, Vrm</t>
+          <t>Väster Naturreservatet Kullarna, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>386238.2664441454</v>
+        <v>385984</v>
       </c>
       <c r="R18" t="n">
-        <v>6713581.403842147</v>
+        <v>6713398</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2680,27 +2333,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Plockhugget för länge sedan (1800-tal?). Brandstubbar.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2709,88 +2352,66 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm, Lars Tidemalm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>102936293</v>
+        <v>112551706</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kullarna NR, V om, Vrm</t>
+          <t>Väster Naturreservatet Kullarna, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>386224.1805757729</v>
+        <v>386181</v>
       </c>
       <c r="R19" t="n">
-        <v>6713588.248658027</v>
+        <v>6713498</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2814,27 +2435,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Plockhugget för länge sedan (1800-tal?). Brandstubbar.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2843,88 +2454,67 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm, Lars Tidemalm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>102936449</v>
+        <v>80108359</v>
       </c>
       <c r="B20" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kullarna NR, V om, Vrm</t>
+          <t>Kullarna , Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>386176.8997174254</v>
+        <v>386017</v>
       </c>
       <c r="R20" t="n">
-        <v>6713527.702095188</v>
+        <v>6713418</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2948,27 +2538,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Plockhugget för länge sedan (1800-tal?). Brandstubbar.</t>
+          <t>Björkstubbe</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2977,56 +2557,50 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm, Lars Tidemalm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>102936232</v>
+        <v>80108094</v>
       </c>
       <c r="B21" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3034,31 +2608,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kullarna NR, V om, Vrm</t>
+          <t>Kullarna , Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>386259.9630403839</v>
+        <v>385971</v>
       </c>
       <c r="R21" t="n">
-        <v>6713596.967661057</v>
+        <v>6713385</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3082,27 +2647,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Barrnaturskog. Plockhugget för länge sedan (1800-tal?). Brandstubbar.</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3111,34 +2661,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm, Lars Tidemalm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>102936443</v>
+        <v>102936165</v>
       </c>
       <c r="B22" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3165,7 +2709,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3186,10 +2730,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>386188.6037164537</v>
+        <v>386258</v>
       </c>
       <c r="R22" t="n">
-        <v>6713539.149706484</v>
+        <v>6713621</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3219,19 +2763,9 @@
           <t>2022-08-10</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3264,15 +2798,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>102936202</v>
+        <v>102936181</v>
       </c>
       <c r="B23" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3299,7 +2828,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3320,13 +2849,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>386256.0681954787</v>
+        <v>386255</v>
       </c>
       <c r="R23" t="n">
-        <v>6713598.567513851</v>
+        <v>6713614</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3353,19 +2882,9 @@
           <t>2022-08-10</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3398,15 +2917,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>102936424</v>
+        <v>102936202</v>
       </c>
       <c r="B24" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3433,7 +2947,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3454,13 +2968,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>386218.035851235</v>
+        <v>386256</v>
       </c>
       <c r="R24" t="n">
-        <v>6713581.057034052</v>
+        <v>6713599</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3487,19 +3001,9 @@
           <t>2022-08-10</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3532,15 +3036,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>102936253</v>
+        <v>102936232</v>
       </c>
       <c r="B25" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3588,10 +3087,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>386267.8147573028</v>
+        <v>386260</v>
       </c>
       <c r="R25" t="n">
-        <v>6713595.73544201</v>
+        <v>6713597</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3621,19 +3120,9 @@
           <t>2022-08-10</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3666,50 +3155,61 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>105127730</v>
+        <v>102936253</v>
       </c>
       <c r="B26" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Väster om Kullarna, Vrm</t>
+          <t>Kullarna NR, V om, Vrm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>386192.0021354585</v>
+        <v>386268</v>
       </c>
       <c r="R26" t="n">
-        <v>6713521.809664883</v>
+        <v>6713596</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3736,22 +3236,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-12-07</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-12-07</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-10</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Plockhugget för länge sedan (1800-tal?). Brandstubbar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3760,71 +3255,83 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Rolf Tidemalm</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Rolf Tidemalm, Lars Tidemalm</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>105127729</v>
+        <v>102936273</v>
       </c>
       <c r="B27" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Väster om Kullarna, Vrm</t>
+          <t>Kullarna NR, V om, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>386169.8935760917</v>
+        <v>386238</v>
       </c>
       <c r="R27" t="n">
-        <v>6713524.476539738</v>
+        <v>6713581</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3848,22 +3355,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-12-07</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-12-07</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-10</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Plockhugget för länge sedan (1800-tal?). Brandstubbar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3872,71 +3374,83 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Rolf Tidemalm</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Rolf Tidemalm, Lars Tidemalm</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112551662</v>
+        <v>102936293</v>
       </c>
       <c r="B28" t="n">
-        <v>81483</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Väster Naturreservatet Kullarna, Vrm</t>
+          <t>Kullarna NR, V om, Vrm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>386234</v>
+        <v>386224</v>
       </c>
       <c r="R28" t="n">
-        <v>6713574</v>
+        <v>6713588</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3960,12 +3474,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>2022-08-10</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Plockhugget för länge sedan (1800-tal?). Brandstubbar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3974,33 +3493,29 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Rolf Tidemalm</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Lars Tidemalm, Rolf Tidemalm</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112551681</v>
+        <v>102936371</v>
       </c>
       <c r="B29" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4025,20 +3540,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Väster Naturreservatet Kullarna, Vrm</t>
+          <t>Kullarna NR, V om, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>386295</v>
+        <v>386221</v>
       </c>
       <c r="R29" t="n">
-        <v>6713615</v>
+        <v>6713586</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4062,12 +3593,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>2022-08-10</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Plockhugget för länge sedan (1800-tal?). Brandstubbar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4076,71 +3612,83 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Rolf Tidemalm</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Rolf Tidemalm, Lars Tidemalm</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112551702</v>
+        <v>102936383</v>
       </c>
       <c r="B30" t="n">
-        <v>78809</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Väster Naturreservatet Kullarna, Vrm</t>
+          <t>Kullarna NR, V om, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>385983</v>
+        <v>386231</v>
       </c>
       <c r="R30" t="n">
-        <v>6713397</v>
+        <v>6713580</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4164,17 +3712,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På asp.</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4183,71 +3726,83 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Rolf Tidemalm</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Rolf Tidemalm, Lars Tidemalm</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112551704</v>
+        <v>102936424</v>
       </c>
       <c r="B31" t="n">
-        <v>78767</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Väster Naturreservatet Kullarna, Vrm</t>
+          <t>Kullarna NR, V om, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>385983</v>
+        <v>386218</v>
       </c>
       <c r="R31" t="n">
-        <v>6713397</v>
+        <v>6713581</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4271,17 +3826,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>Barrnaturskog. Plockhugget för länge sedan (1800-tal?). Brandstubbar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4290,71 +3845,83 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Rolf Tidemalm</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Rolf Tidemalm, Lars Tidemalm</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112551671</v>
+        <v>102936443</v>
       </c>
       <c r="B32" t="n">
-        <v>78809</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Väster Naturreservatet Kullarna, Vrm</t>
+          <t>Kullarna NR, V om, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>386308</v>
+        <v>386189</v>
       </c>
       <c r="R32" t="n">
-        <v>6713631</v>
+        <v>6713539</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4378,17 +3945,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>Barrnaturskog. Plockhugget för länge sedan (1800-tal?). Brandstubbar.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4397,71 +3964,83 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Rolf Tidemalm</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Rolf Tidemalm, Lars Tidemalm</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112551673</v>
+        <v>102936449</v>
       </c>
       <c r="B33" t="n">
-        <v>78767</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Väster Naturreservatet Kullarna, Vrm</t>
+          <t>Kullarna NR, V om, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>386308</v>
+        <v>386177</v>
       </c>
       <c r="R33" t="n">
-        <v>6713631</v>
+        <v>6713528</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4485,17 +4064,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>Barrnaturskog. Plockhugget för länge sedan (1800-tal?). Brandstubbar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4504,71 +4083,83 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Rolf Tidemalm</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Rolf Tidemalm, Lars Tidemalm</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112551679</v>
+        <v>102938702</v>
       </c>
       <c r="B34" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Väster Naturreservatet Kullarna, Vrm</t>
+          <t>Kullarna NR, V om, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>386245</v>
+        <v>386177</v>
       </c>
       <c r="R34" t="n">
-        <v>6713552</v>
+        <v>6713519</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4592,12 +4183,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>2022-08-10</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Plockhugget för länga sedan (1800-tal?). Brandstubbar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4606,55 +4202,51 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Rolf Tidemalm</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Rolf Tidemalm, Lars Tidemalm</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112551677</v>
+        <v>112551681</v>
       </c>
       <c r="B35" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4664,10 +4256,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>386047</v>
+        <v>386295</v>
       </c>
       <c r="R35" t="n">
-        <v>6713439</v>
+        <v>6713615</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4723,6 +4315,806 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>80108318</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kullarna , Vrm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>385985</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6713400</v>
+      </c>
+      <c r="S36" t="n">
+        <v>4</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2019-09-26</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2019-09-26</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>80108366</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kullarna , Vrm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>386017</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6713418</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2019-09-26</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2019-09-26</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Björkstubbe</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>80109644</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kullarna , Vrm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>386058</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6713415</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2019-09-26</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2019-09-26</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>80110315</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kullarna , Vrm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>386298</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6713643</v>
+      </c>
+      <c r="S39" t="n">
+        <v>4</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2019-09-26</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2019-09-26</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>105127731</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Väster om Kullarna, Vrm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>386305</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6713654</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2022-12-07</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2022-12-07</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>112551673</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Väster Naturreservatet Kullarna, Vrm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>386309</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6713632</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2022-08-24</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2022-08-24</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På asp.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>112551704</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Väster Naturreservatet Kullarna, Vrm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>385984</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6713398</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2022-08-24</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2022-08-24</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På asp.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>112551708</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Väster Naturreservatet Kullarna, Vrm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>386181</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6713498</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2022-08-24</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2022-08-24</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På asp.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22230-2022 artfynd.xlsx
+++ b/artfynd/A 22230-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80108615</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80109004</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -969,6 +984,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551662</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1066,6 +1086,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105127729</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1164,6 +1189,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102804581</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1261,6 +1291,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105127730</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1358,6 +1393,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551677</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1455,6 +1495,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551679</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1553,6 +1598,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80108465</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1651,6 +1701,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80110283</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1754,6 +1809,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80108313</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1857,6 +1917,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80109640</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1960,6 +2025,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80110304</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2066,6 +2136,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102936113</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2163,6 +2238,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105127732</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2265,6 +2345,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551671</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2367,6 +2452,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551702</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2469,6 +2559,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551706</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2572,6 +2667,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80108359</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2676,6 +2776,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80108094</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2795,6 +2900,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102936165</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2914,6 +3024,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102936181</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3033,6 +3148,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102936202</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3152,6 +3272,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102936232</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3271,6 +3396,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102936253</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3390,6 +3520,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102936273</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3509,6 +3644,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102936293</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3628,6 +3768,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102936371</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3742,6 +3887,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102936383</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3861,6 +4011,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102936424</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3980,6 +4135,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102936443</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4099,6 +4259,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102936449</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4218,6 +4383,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102938702</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4315,6 +4485,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551681</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4413,6 +4588,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80108318</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4516,6 +4696,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80108366</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4614,6 +4799,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80109644</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4712,6 +4902,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80110315</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4809,6 +5004,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105127731</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4911,6 +5111,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551673</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5013,6 +5218,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551704</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5115,8 +5325,57 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551708</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>